--- a/Nassau_Clustering_Results.xlsx
+++ b/Nassau_Clustering_Results.xlsx
@@ -1,35 +1,113 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adity\Nassau-Candy-Data-Analysis\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B890848-3F4C-42F9-BD29-3AA1CB420ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Product Clusters" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cluster Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Product Clusters" sheetId="1" r:id="rId1"/>
+    <sheet name="Cluster Summary" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+  <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>Total_Sales</t>
+  </si>
+  <si>
+    <t>Total_Units</t>
+  </si>
+  <si>
+    <t>Total_Cost</t>
+  </si>
+  <si>
+    <t>Average_Lead_Time</t>
+  </si>
+  <si>
+    <t>Average_Sales</t>
+  </si>
+  <si>
+    <t>Cluster</t>
+  </si>
+  <si>
+    <t>Everlasting Gobstopper</t>
+  </si>
+  <si>
+    <t>Hair Toffee</t>
+  </si>
+  <si>
+    <t>SweeTARTS</t>
+  </si>
+  <si>
+    <t>Laffy Taffy</t>
+  </si>
+  <si>
+    <t>Wonka Bar - Triple Dazzle Caramel</t>
+  </si>
+  <si>
+    <t>Wonka Bar -Scrumdiddlyumptious</t>
+  </si>
+  <si>
+    <t>Wonka Bar - Milk Chocolate</t>
+  </si>
+  <si>
+    <t>Wonka Bar - Fudge Mallows</t>
+  </si>
+  <si>
+    <t>Wonka Bar - Nutty Crunch Surprise</t>
+  </si>
+  <si>
+    <t>Kazookles</t>
+  </si>
+  <si>
+    <t>Wonka Gum</t>
+  </si>
+  <si>
+    <t>Fizzy Lifting Drinks</t>
+  </si>
+  <si>
+    <t>Nerds</t>
+  </si>
+  <si>
+    <t>Fun Dip</t>
+  </si>
+  <si>
+    <t>Lickable Wallpaper</t>
+  </si>
+  <si>
+    <t>Products</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -48,80 +126,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -409,423 +428,384 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Product Name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Total_Sales</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Total_Units</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Total_Cost</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Average_Lead_Time</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Average_Sales</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Cluster</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Everlasting Gobstopper</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
         <v>130</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>13</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>26</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>1394.666666666667</v>
       </c>
-      <c r="F2" t="n">
-        <v>43.33333333333334</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="F2">
+        <v>43.333333333333343</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Hair Toffee</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
         <v>76.5</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>17</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>17</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>1455.25</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>19.125</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>SweeTARTS</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
         <v>61.5</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>41</v>
       </c>
-      <c r="D4" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="D4">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="E4">
         <v>1383.5</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>6.15</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Laffy Taffy</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
         <v>53.73</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>27</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>20.25</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>1383.1</v>
       </c>
-      <c r="F5" t="n">
-        <v>5.372999999999999</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="F5">
+        <v>5.3729999999999993</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Wonka Bar - Triple Dazzle Caramel</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
         <v>28485</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>7596</v>
       </c>
-      <c r="D6" t="n">
-        <v>9874.799999999999</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1325.661042183623</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="D6">
+        <v>9874.7999999999993</v>
+      </c>
+      <c r="E6">
+        <v>1325.6610421836231</v>
+      </c>
+      <c r="F6">
         <v>14.13647642679901</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>2</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Wonka Bar -Scrumdiddlyumptious</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>27874.8</v>
-      </c>
-      <c r="C7" t="n">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7">
+        <v>27874.799999999999</v>
+      </c>
+      <c r="C7">
         <v>7743</v>
       </c>
-      <c r="D7" t="n">
-        <v>8517.299999999999</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1320.641957364341</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="D7">
+        <v>8517.2999999999993</v>
+      </c>
+      <c r="E7">
+        <v>1320.6419573643409</v>
+      </c>
+      <c r="F7">
         <v>13.50523255813953</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>2</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Wonka Bar - Milk Chocolate</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8">
         <v>26867.75</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>8267</v>
       </c>
-      <c r="D8" t="n">
-        <v>9424.379999999999</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1316.764623303697</v>
-      </c>
-      <c r="F8" t="n">
+      <c r="D8">
+        <v>9424.3799999999992</v>
+      </c>
+      <c r="E8">
+        <v>1316.7646233036969</v>
+      </c>
+      <c r="F8">
         <v>12.57264857276556</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>2</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Wonka Bar - Fudge Mallows</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>24890.4</v>
-      </c>
-      <c r="C9" t="n">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <v>24890.400000000001</v>
+      </c>
+      <c r="C9">
         <v>6914</v>
       </c>
-      <c r="D9" t="n">
-        <v>8296.799999999999</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D9">
+        <v>8296.7999999999993</v>
+      </c>
+      <c r="E9">
         <v>1314.24202420242</v>
       </c>
-      <c r="F9" t="n">
-        <v>13.69108910891089</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="F9">
+        <v>13.691089108910891</v>
+      </c>
+      <c r="G9">
         <v>2</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Wonka Bar - Nutty Crunch Surprise</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
         <v>23574.95</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>6755</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>6755</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>1328.91546961326</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>13.02483425414365</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>2</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Kazookles</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11">
         <v>1205.75</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>371</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>1113</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>1272.989583333333</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>12.55989583333333</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>3</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Wonka Gum</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12">
         <v>597.5</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>478</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>286.8</v>
       </c>
-      <c r="E12" t="n">
-        <v>1306.525</v>
-      </c>
-      <c r="F12" t="n">
+      <c r="E12">
+        <v>1306.5250000000001</v>
+      </c>
+      <c r="F12">
         <v>4.979166666666667</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>3</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Fizzy Lifting Drinks</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13">
         <v>78.75</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>21</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>31.5</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>1273.5</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>13.125</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>3</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Nerds</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14">
         <v>15</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>10</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>8</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>1274</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>3.75</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>3</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Fun Dip</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15">
         <v>12</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>8</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>7.2</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>1272.666666666667</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>4</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>3</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Lickable Wallpaper</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16">
         <v>7860</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>393</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>3930</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>1339.13829787234</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>83.61702127659575</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>4</v>
       </c>
     </row>
@@ -835,123 +815,115 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Cluster</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Products</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Total_Sales</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Total_Units</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Average_Lead_Time</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Average_Sales</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="n">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
         <v>321.73</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>98</v>
       </c>
-      <c r="E2" t="n">
-        <v>1404.129166666667</v>
-      </c>
-      <c r="F2" t="n">
-        <v>18.49533333333333</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="E2">
+        <v>1404.1291666666671</v>
+      </c>
+      <c r="F2">
+        <v>18.495333333333331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>5</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>131692.9</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>37275</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>1321.245023333468</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>13.38605618415173</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>5</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>1909</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>888</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>1279.93625</v>
       </c>
-      <c r="F4" t="n">
-        <v>7.6828125</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="F4">
+        <v>7.6828124999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>7860</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>393</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>1339.13829787234</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>83.61702127659575</v>
       </c>
     </row>
